--- a/test/fixtures/xlsx/reference-keys/reference-keys.xlsx
+++ b/test/fixtures/xlsx/reference-keys/reference-keys.xlsx
@@ -12,47 +12,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="51">
-  <si>
-    <t xml:space="preserve">~~table:Animation~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
+  <si>
+    <t xml:space="preserve">:table Animation</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed by name.</t>
   </si>
   <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index, a string</t>
   </si>
   <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">cs</t>
   </si>
   <si>
     <t xml:space="preserve">Blend</t>
   </si>
   <si>
+    <t xml:space="preserve">float</t>
+  </si>
+  <si>
     <t xml:space="preserve">anything</t>
   </si>
   <si>
-    <t xml:space="preserve">float</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pad1</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">padding, so every table is one width</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pad2</t>
   </si>
   <si>
@@ -68,18 +77,18 @@
     <t xml:space="preserve">0.2</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Ledger~~</t>
+    <t xml:space="preserve">:table Ledger</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed by a 64-bit id.</t>
   </si>
   <si>
+    <t xml:space="preserve">bigint</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index, wider than an int</t>
   </si>
   <si>
-    <t xml:space="preserve">bigint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Note</t>
   </si>
   <si>
@@ -95,18 +104,18 @@
     <t xml:space="preserve">second</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Art~~</t>
+    <t xml:space="preserve">:table Art</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed by a uuid.</t>
   </si>
   <si>
+    <t xml:space="preserve">uuid</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index, a uuid</t>
   </si>
   <si>
-    <t xml:space="preserve">uuid</t>
-  </si>
-  <si>
     <t xml:space="preserve">Path</t>
   </si>
   <si>
@@ -122,7 +131,7 @@
     <t xml:space="preserve">b.png</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Clip~~</t>
+    <t xml:space="preserve">:table Clip</t>
   </si>
   <si>
     <t xml:space="preserve">Points at all three at once.</t>
@@ -134,31 +143,28 @@
     <t xml:space="preserve">Anim</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Animation</t>
+  </si>
+  <si>
     <t xml:space="preserve">a string-keyed target</t>
   </si>
   <si>
-    <t xml:space="preserve">foreign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Animation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Entry</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Ledger</t>
+  </si>
+  <si>
     <t xml:space="preserve">a bigint-keyed target</t>
   </si>
   <si>
-    <t xml:space="preserve">Ledger</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cover</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Art</t>
+  </si>
+  <si>
     <t xml:space="preserve">a uuid-keyed target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -209,79 +215,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:AC10"/>
+  <dimension ref="B2:AD8"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
       </c>
       <c r="R2" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
+        <v>31</v>
       </c>
       <c r="Z2" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" t="s">
+        <v>16</v>
       </c>
       <c r="R3" t="s">
-        <v>28</v>
+        <v>2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" t="s">
+        <v>13</v>
+      </c>
+      <c r="V3" t="s">
+        <v>16</v>
       </c>
       <c r="Z3" t="s">
-        <v>37</v>
+        <v>2</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
       </c>
       <c r="R4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="V4" t="s">
+        <v>14</v>
       </c>
       <c r="Z4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="AB4" t="s">
         <v>43</v>
@@ -289,49 +364,61 @@
       <c r="AC4" t="s">
         <v>46</v>
       </c>
+      <c r="AD4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M5" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="N5" t="s">
+        <v>15</v>
       </c>
       <c r="R5" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="S5" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="T5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U5" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="V5" t="s">
+        <v>15</v>
       </c>
       <c r="Z5" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AB5" t="s">
         <v>44</v>
@@ -339,255 +426,170 @@
       <c r="AC5" t="s">
         <v>47</v>
       </c>
+      <c r="AD5" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M6" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="N6" t="s">
+        <v>9</v>
       </c>
       <c r="R6" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="S6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="V6" t="s">
+        <v>9</v>
       </c>
       <c r="Z6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="AB6" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="s">
-        <v>41</v>
+        <v>9</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="M7" t="s">
-        <v>5</v>
-      </c>
-      <c r="R7" t="s">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="N7" t="s">
+        <v>18</v>
       </c>
       <c r="S7" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T7" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="U7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="V7" t="s">
+        <v>18</v>
       </c>
       <c r="AA7" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AB7" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="s">
-        <v>48</v>
+        <v>26</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="L8" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="M8" t="s">
-        <v>6</v>
-      </c>
-      <c r="R8" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="N8" t="s">
+        <v>18</v>
       </c>
       <c r="S8" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="T8" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="U8" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="V8" t="s">
+        <v>18</v>
       </c>
       <c r="AA8" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="AB8" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AC8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" t="s">
-        <v>15</v>
-      </c>
-      <c r="R9" t="s">
-        <v>32</v>
-      </c>
-      <c r="S9" t="s">
-        <v>33</v>
-      </c>
-      <c r="T9" t="s">
-        <v>15</v>
-      </c>
-      <c r="U9" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" t="s">
-        <v>15</v>
-      </c>
-      <c r="R10" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" t="s">
-        <v>35</v>
-      </c>
-      <c r="T10" t="s">
-        <v>15</v>
-      </c>
-      <c r="U10" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>34</v>
+        <v>28</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
